--- a/src/main/Test_cases/LuxepolisTest_Cases.xlsx
+++ b/src/main/Test_cases/LuxepolisTest_Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="125">
   <si>
     <t>Add to cart</t>
   </si>
@@ -1652,7 +1652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1775,6 +1775,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
@@ -2154,7 +2160,7 @@
       <c r="G3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="44" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="41" t="s">

--- a/src/main/Test_cases/LuxepolisTest_Cases.xlsx
+++ b/src/main/Test_cases/LuxepolisTest_Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="125">
   <si>
     <t>Add to cart</t>
   </si>
@@ -1652,7 +1652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1784,6 +1784,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2160,8 +2163,8 @@
       <c r="G3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="44" t="s">
-        <v>14</v>
+      <c r="H3" s="45" t="s">
+        <v>118</v>
       </c>
       <c r="I3" s="41" t="s">
         <v>118</v>

--- a/src/main/Test_cases/LuxepolisTest_Cases.xlsx
+++ b/src/main/Test_cases/LuxepolisTest_Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="125">
   <si>
     <t>Add to cart</t>
   </si>
@@ -1652,7 +1652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1787,6 +1787,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2163,8 +2169,8 @@
       <c r="G3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="45" t="s">
-        <v>118</v>
+      <c r="H3" s="47" t="s">
+        <v>14</v>
       </c>
       <c r="I3" s="41" t="s">
         <v>118</v>

--- a/src/main/Test_cases/LuxepolisTest_Cases.xlsx
+++ b/src/main/Test_cases/LuxepolisTest_Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="125">
   <si>
     <t>Add to cart</t>
   </si>
@@ -1652,7 +1652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1787,6 +1787,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
@@ -2169,7 +2184,7 @@
       <c r="G3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="H3" s="52" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="41" t="s">

--- a/src/main/Test_cases/LuxepolisTest_Cases.xlsx
+++ b/src/main/Test_cases/LuxepolisTest_Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="125">
   <si>
     <t>Add to cart</t>
   </si>
@@ -1652,7 +1652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1799,6 +1799,48 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="true" applyAlignment="1">
@@ -2184,7 +2226,7 @@
       <c r="G3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H3" s="52" t="s">
+      <c r="H3" s="66" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="41" t="s">

--- a/src/main/Test_cases/LuxepolisTest_Cases.xlsx
+++ b/src/main/Test_cases/LuxepolisTest_Cases.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B8948114-B9C7-4023-904A-66EDACAE6CC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{BC266738-23BC-43C7-93F6-478564A44E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="133">
   <si>
     <t>Test Caese ID</t>
   </si>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t>Actual Result</t>
-  </si>
-  <si>
-    <t>Status</t>
   </si>
   <si>
     <t>Verify online payment/COD functionality</t>
@@ -1503,10 +1500,10 @@
     <t>PRFW2050</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>COD option showing enable</t>
+    <t>Test Case Status</t>
+  </si>
+  <si>
+    <t>Test Cases Condition</t>
   </si>
 </sst>
 </file>
@@ -1514,7 +1511,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1565,8 +1562,21 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1598,6 +1608,22 @@
       </patternFill>
     </fill>
     <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor indexed="17"/>
       </patternFill>
@@ -1606,27 +1632,6 @@
       <patternFill patternType="solid">
         <fgColor indexed="17"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
       </patternFill>
     </fill>
   </fills>
@@ -1654,30 +1659,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="FFCCCCCC"/>
@@ -1688,26 +1669,6 @@
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1726,11 +1687,77 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1738,790 +1765,127 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyFill="true">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyFill="true">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyFill="true">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyFill="true">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1" applyFill="true">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2803,971 +2167,968 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y50"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Y52"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="4" width="17.28515625"/>
-    <col min="2" max="2" customWidth="true" style="4" width="38.85546875"/>
-    <col min="3" max="3" customWidth="true" style="4" width="41.42578125"/>
-    <col min="4" max="4" customWidth="true" style="4" width="32.28515625"/>
-    <col min="5" max="5" customWidth="true" style="4" width="20.7109375"/>
-    <col min="6" max="6" customWidth="true" style="4" width="38.7109375"/>
-    <col min="7" max="7" customWidth="true" style="4" width="52.28515625"/>
-    <col min="8" max="8" customWidth="true" style="4" width="22.140625"/>
-    <col min="9" max="16384" style="4" width="8.85546875"/>
+    <col min="1" max="1" customWidth="true" style="25" width="17.33203125"/>
+    <col min="2" max="2" customWidth="true" style="7" width="38.88671875"/>
+    <col min="3" max="3" customWidth="true" style="7" width="41.44140625"/>
+    <col min="4" max="4" customWidth="true" style="7" width="32.33203125"/>
+    <col min="5" max="5" customWidth="true" style="7" width="20.6640625"/>
+    <col min="6" max="6" customWidth="true" style="7" width="38.6640625"/>
+    <col min="7" max="7" customWidth="true" style="7" width="52.33203125"/>
+    <col min="8" max="8" customWidth="true" style="7" width="22.109375"/>
+    <col min="9" max="9" customWidth="true" style="26" width="29.109375"/>
+    <col min="10" max="16384" style="1" width="8.88671875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:25" s="4" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2" s="23"/>
+      <c r="B2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="32"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="24"/>
+    </row>
+    <row r="3" spans="1:25" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-    </row>
-    <row r="3" spans="1:25" ht="135" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="13" t="s">
+    </row>
+    <row r="4" spans="1:25" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:25" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:25" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="30"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:25" ht="58.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="30"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A10" s="30"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="11"/>
-    </row>
-    <row r="7" spans="1:25" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="B11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:25" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="30"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:25" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:25" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:25" ht="48" x14ac:dyDescent="0.3">
+      <c r="A13" s="30"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A14" s="30"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2" t="s">
+      <c r="E14" s="11"/>
+      <c r="F14" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="G14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A15" s="30"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:25" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="30"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" ht="58.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="30"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:25" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2" t="s">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="1:10" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="30"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="1:10" ht="48" x14ac:dyDescent="0.3">
+      <c r="A20" s="30"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2" t="s">
+      <c r="H20" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="30"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="30"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+    </row>
+    <row r="23" spans="1:10" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="30"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+    </row>
+    <row r="24" spans="1:10" ht="48" x14ac:dyDescent="0.3">
+      <c r="A24" s="30"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:25" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="2" t="s">
+      <c r="G24" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="2" t="s">
+      <c r="D25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+    </row>
+    <row r="26" spans="1:10" ht="60" x14ac:dyDescent="0.3">
+      <c r="A26" s="30"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="2" t="s">
+      <c r="G26" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="30"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="30"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="2" t="s">
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="30"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+    </row>
+    <row r="30" spans="1:10" ht="48" x14ac:dyDescent="0.3">
+      <c r="A30" s="30"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="11"/>
+      <c r="F30" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="2" t="s">
+      <c r="G30" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="B31" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+    </row>
+    <row r="32" spans="1:10" ht="36" x14ac:dyDescent="0.3">
+      <c r="A32" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:10" ht="59.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="11"/>
-    </row>
-    <row r="33" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="B33" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C33" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="11"/>
+      <c r="E33" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" s="16"/>
+      <c r="I33" s="31"/>
+    </row>
+    <row r="34" spans="1:10" ht="59.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="11"/>
+      <c r="E34" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="16"/>
+      <c r="I34" s="31"/>
+    </row>
+    <row r="35" spans="1:10" ht="59.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" s="11"/>
+      <c r="E35" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35" s="16"/>
+      <c r="I35" s="31"/>
+    </row>
+    <row r="36" spans="1:10" ht="58.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="11"/>
+      <c r="E36" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="16"/>
+      <c r="I36" s="31"/>
+    </row>
+    <row r="37" spans="1:10" ht="82.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="16"/>
+      <c r="I37" s="31"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="27"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+    </row>
+    <row r="39" spans="1:10" ht="105" x14ac:dyDescent="0.3">
+      <c r="A39" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="H39" s="16"/>
+      <c r="I39" s="31"/>
+    </row>
+    <row r="40" spans="1:10" ht="105" x14ac:dyDescent="0.3">
+      <c r="A40" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="16"/>
+      <c r="I40" s="31"/>
+    </row>
+    <row r="41" spans="1:10" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" s="16"/>
+      <c r="I41" s="31"/>
+    </row>
+    <row r="42" spans="1:10" ht="82.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="H42" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" t="s" s="33">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="94.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G43" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="H43" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" t="s" s="36">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="94.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H44" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" t="s" s="39">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+    </row>
+    <row r="46" spans="1:10" ht="114" x14ac:dyDescent="0.3">
+      <c r="A46" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H46" s="16"/>
+      <c r="I46" s="31"/>
+    </row>
+    <row r="47" spans="1:10" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E47" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H33" s="252" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" t="s" s="253">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H34" s="254" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" t="s" s="255">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="F35" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H35" s="256" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" t="s" s="257">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="F36" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H36" s="258" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" t="s" s="259">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>131</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H37" s="260" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" t="s" s="261">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-    </row>
-    <row r="39" spans="1:8" ht="108.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B39" s="14" t="s">
+      <c r="F47" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H47" s="16"/>
+      <c r="I47" s="31"/>
+    </row>
+    <row r="48" spans="1:10" ht="91.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G39" s="241" t="s">
-        <v>85</v>
-      </c>
-      <c r="H39" s="240" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="108.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H40" s="242" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H41" s="243" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G42" s="226" t="s">
-        <v>85</v>
-      </c>
-      <c r="H42" s="225" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G43" s="228" t="s">
-        <v>85</v>
-      </c>
-      <c r="H43" s="227" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H44" s="229" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-    </row>
-    <row r="46" spans="1:8" ht="120" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B46" s="2" t="s">
+      <c r="D48" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F46" s="14" t="s">
+      <c r="E48" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H48" s="16"/>
+      <c r="I48" s="31"/>
+    </row>
+    <row r="49" spans="1:10" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H46" s="221" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H47" s="220" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H48" s="224" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="59.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="H49" s="16"/>
+      <c r="I49" s="31"/>
+    </row>
+    <row r="50" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H49" s="222" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="B50" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F50" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F50" s="5" t="s">
+      <c r="G50" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G50" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H50" s="223" t="s">
-        <v>16</v>
-      </c>
+      <c r="H50" s="16"/>
+      <c r="I50" s="31"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H51" s="8"/>
+      <c r="I51" s="31"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H52" s="8"/>
+      <c r="I52" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/src/main/Test_cases/LuxepolisTest_Cases.xlsx
+++ b/src/main/Test_cases/LuxepolisTest_Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="133">
   <si>
     <t>Test Caese ID</t>
   </si>
@@ -1765,7 +1765,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1886,6 +1886,36 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="true" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2715,8 +2745,12 @@
       <c r="G33" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="H33" s="16"/>
-      <c r="I33" s="31"/>
+      <c r="H33" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="I33" s="42" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="34" spans="1:10" ht="59.4" x14ac:dyDescent="0.3">
       <c r="A34" s="29" t="s">
@@ -2738,8 +2772,12 @@
       <c r="G34" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="H34" s="16"/>
-      <c r="I34" s="31"/>
+      <c r="H34" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="44" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="35" spans="1:10" ht="59.4" x14ac:dyDescent="0.3">
       <c r="A35" s="29" t="s">
@@ -2761,8 +2799,12 @@
       <c r="G35" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="16"/>
-      <c r="I35" s="31"/>
+      <c r="H35" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="I35" s="46" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="36" spans="1:10" ht="58.8" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
@@ -2784,8 +2826,12 @@
       <c r="G36" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="16"/>
-      <c r="I36" s="31"/>
+      <c r="H36" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="48" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="37" spans="1:10" ht="82.2" x14ac:dyDescent="0.3">
       <c r="A37" s="29" t="s">
@@ -2809,8 +2855,12 @@
       <c r="G37" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H37" s="16"/>
-      <c r="I37" s="31"/>
+      <c r="H37" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="I37" s="50" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="27"/>
